--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_SENCILLO.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_SENCILLO.xlsx
@@ -3374,11 +3374,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="73892631"/>
-        <c:axId val="7186876"/>
+        <c:axId val="7221499"/>
+        <c:axId val="67562108"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="73892631"/>
+        <c:axId val="7221499"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -3412,7 +3412,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7186876"/>
+        <c:crossAx val="67562108"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -3424,7 +3424,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="7186876"/>
+        <c:axId val="67562108"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3467,7 +3467,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73892631"/>
+        <c:crossAx val="7221499"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5240,11 +5240,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="74643288"/>
-        <c:axId val="30922344"/>
+        <c:axId val="22751911"/>
+        <c:axId val="96360162"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="74643288"/>
+        <c:axId val="22751911"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5276,7 +5276,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="30922344"/>
+        <c:crossAx val="96360162"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -5287,7 +5287,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="30922344"/>
+        <c:axId val="96360162"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5363,7 +5363,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74643288"/>
+        <c:crossAx val="22751911"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8920,7 +8920,7 @@
       </c>
       <c r="AW20" s="31" t="n">
         <f aca="false">LOOKUP(AW19,$A$3:$A$2973,$B$3:$B$2973)</f>
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="AX20" s="31" t="n">
         <f aca="false">LOOKUP(AX19,$A$3:$A$2973,$B$3:$B$2973)</f>
@@ -9178,7 +9178,7 @@
       </c>
       <c r="AH22" s="22" t="n">
         <f aca="false">+(S23/R23-1)</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AI22" s="9"/>
       <c r="AJ22" s="9"/>
@@ -9190,7 +9190,7 @@
       <c r="AP22" s="9"/>
       <c r="AQ22" s="23" t="n">
         <f aca="false">+(S23/P23-1)/COUNTA(AE22:AP22)*12</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
       <c r="AV22" s="6" t="s">
         <v>26</v>
@@ -9244,7 +9244,7 @@
       </c>
       <c r="S23" s="3" t="n">
         <f aca="false">+B249</f>
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="U23" s="19"/>
       <c r="Y23" s="19"/>
@@ -9742,23 +9742,23 @@
       </c>
       <c r="AX29" s="41" t="n">
         <f aca="false">($AW20/AX20-1)/(AW19-AX19)*30</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AY29" s="41" t="n">
         <f aca="false">$AW20/AY20-1</f>
-        <v>-0.248750231235289</v>
+        <v>-0.237979628862347</v>
       </c>
       <c r="AZ29" s="41" t="n">
         <f aca="false">$AW20/AZ20-1</f>
-        <v>-0.239809516977627</v>
+        <v>-0.228910732364632</v>
       </c>
       <c r="BA29" s="41" t="n">
         <f aca="false">$AW20/BA20-1</f>
-        <v>-0.220741912237796</v>
+        <v>-0.209569757039683</v>
       </c>
       <c r="BB29" s="41" t="n">
         <f aca="false">+AQ87</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
       <c r="BC29" s="42"/>
       <c r="BD29" s="27"/>
@@ -14728,7 +14728,7 @@
       </c>
       <c r="AH87" s="52" t="n">
         <f aca="false">+AH22</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AI87" s="52"/>
       <c r="AJ87" s="52"/>
@@ -14740,7 +14740,7 @@
       <c r="AP87" s="52"/>
       <c r="AQ87" s="52" t="n">
         <f aca="false">+AQ22</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="88" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20981,15 +20981,15 @@
         <v>46142</v>
       </c>
       <c r="B249" s="3" t="n">
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="C249" s="25" t="n">
         <f aca="false">(B249/B248-1)/(A249-A248)*30</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="D249" s="19" t="n">
         <f aca="false">+D248*(1+C249)</f>
-        <v>161.013148761713</v>
+        <v>163.321580223834</v>
       </c>
       <c r="F249" s="17" t="n">
         <v>46142</v>
@@ -21121,23 +21121,23 @@
       </c>
       <c r="T2" s="77" t="n">
         <f aca="false">+'Datos ICP (2)'!AX29</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="U2" s="77" t="n">
         <f aca="false">+'Datos ICP (2)'!AY29</f>
-        <v>-0.248750231235289</v>
+        <v>-0.237979628862347</v>
       </c>
       <c r="V2" s="77" t="n">
         <f aca="false">+'Datos ICP (2)'!AZ29</f>
-        <v>-0.239809516977627</v>
+        <v>-0.228910732364632</v>
       </c>
       <c r="W2" s="77" t="n">
         <f aca="false">+'Datos ICP (2)'!BA29</f>
-        <v>-0.220741912237796</v>
+        <v>-0.209569757039683</v>
       </c>
       <c r="X2" s="77" t="n">
         <f aca="false">+'Datos ICP (2)'!BB29</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23049,7 +23049,7 @@
       </c>
       <c r="H37" s="77" t="n">
         <f aca="false">+'Datos ICP (2)'!AH87</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="I37" s="77"/>
       <c r="J37" s="77"/>
@@ -23061,7 +23061,7 @@
       <c r="P37" s="77"/>
       <c r="Q37" s="77" t="n">
         <f aca="false">+'Datos ICP (2)'!AQ87</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_SENCILLO.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_SENCILLO.xlsx
@@ -3374,11 +3374,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="7221499"/>
-        <c:axId val="67562108"/>
+        <c:axId val="73812041"/>
+        <c:axId val="26171336"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="7221499"/>
+        <c:axId val="73812041"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -3412,7 +3412,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67562108"/>
+        <c:crossAx val="26171336"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -3424,7 +3424,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="67562108"/>
+        <c:axId val="26171336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3467,7 +3467,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7221499"/>
+        <c:crossAx val="73812041"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5240,11 +5240,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="22751911"/>
-        <c:axId val="96360162"/>
+        <c:axId val="51444440"/>
+        <c:axId val="39632262"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="22751911"/>
+        <c:axId val="51444440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5276,7 +5276,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96360162"/>
+        <c:crossAx val="39632262"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -5287,7 +5287,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="96360162"/>
+        <c:axId val="39632262"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5363,7 +5363,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="22751911"/>
+        <c:crossAx val="51444440"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_SENCILLO.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_SENCILLO.xlsx
@@ -3374,11 +3374,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="73812041"/>
-        <c:axId val="26171336"/>
+        <c:axId val="73392896"/>
+        <c:axId val="45208846"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="73812041"/>
+        <c:axId val="73392896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -3412,7 +3412,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26171336"/>
+        <c:crossAx val="45208846"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -3424,7 +3424,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="26171336"/>
+        <c:axId val="45208846"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3467,7 +3467,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73812041"/>
+        <c:crossAx val="73392896"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5240,11 +5240,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="51444440"/>
-        <c:axId val="39632262"/>
+        <c:axId val="74113292"/>
+        <c:axId val="57188921"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="51444440"/>
+        <c:axId val="74113292"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5276,7 +5276,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39632262"/>
+        <c:crossAx val="57188921"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -5287,7 +5287,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="39632262"/>
+        <c:axId val="57188921"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5363,7 +5363,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="51444440"/>
+        <c:crossAx val="74113292"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_SENCILLO.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_SENCILLO.xlsx
@@ -3374,11 +3374,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="73392896"/>
-        <c:axId val="45208846"/>
+        <c:axId val="80882172"/>
+        <c:axId val="75172109"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="73392896"/>
+        <c:axId val="80882172"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -3412,7 +3412,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="45208846"/>
+        <c:crossAx val="75172109"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -3424,7 +3424,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="45208846"/>
+        <c:axId val="75172109"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -3467,7 +3467,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73392896"/>
+        <c:crossAx val="80882172"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5240,11 +5240,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="74113292"/>
-        <c:axId val="57188921"/>
+        <c:axId val="71013500"/>
+        <c:axId val="88847354"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="74113292"/>
+        <c:axId val="71013500"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5276,7 +5276,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="57188921"/>
+        <c:crossAx val="88847354"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -5287,7 +5287,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="57188921"/>
+        <c:axId val="88847354"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5363,7 +5363,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74113292"/>
+        <c:crossAx val="71013500"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
